--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,17 +501,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mascarilla Elvive Dream Liso 300g</t>
+          <t>Crema Tratamiento Elvive Dream Liso x 300 g</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>9898</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9898</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.farmaplus.com.ar/mascarilla-elvive-dream-liso-300g/p</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -598,6 +608,306 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Oleo Extraordinario Elvive x 100 ml</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Serum Antimanchas La Roche Posay Mela B3 x 30 ml</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>151697</v>
+      </c>
+      <c r="G8" t="n">
+        <v>151697</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.farmaplus.com.ar/la-roche-posay-mela-b3-serum-antimanchas-30ml-piel-mixta/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Exfoliante Facial Isdin Suave Acniben x 100 ml</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>61076</v>
+      </c>
+      <c r="C9" t="n">
+        <v>61076</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.farmacity.com/exfoliante-suave-isdin-acniben-x-100-ml/p</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>61076</v>
+      </c>
+      <c r="G9" t="n">
+        <v>61076</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.farmaplus.com.ar/gel-exfoliante-suave-isdin-acniben-teen-skin-100ml/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Protector Solar Facial Nivea Sun Tono Medio Fps 50 x 40 ml</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>37950</v>
+      </c>
+      <c r="G10" t="n">
+        <v>75901</v>
+      </c>
+      <c r="H10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.farmaplus.com.ar/protector-solar-eucerin-sun-cc-cream-fps50-con-color-x-50ml-barr/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gel Limpiador Cetaphil Exfoliante Suave x 236 ml</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>40950</v>
+      </c>
+      <c r="C11" t="n">
+        <v>40950</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.farmacity.com/gel-limpiador-cetaphil-exfoliante-suave-x-236-ml/p</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>40950</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40950</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.farmaplus.com.ar/cetaphil-limpiador-exfoliante-suave-236ml/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aceite Solar Invisible Vichy Capital Soleil Cell Protect Spf 50+ x 200 ml</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Loción Corporal CeraVe Hidratante x 236 ml</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Labial Líquido Maybelline SuperStay Vinyl Ink</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>18144</v>
+      </c>
+      <c r="G14" t="n">
+        <v>32990</v>
+      </c>
+      <c r="H14" t="n">
+        <v>45</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.farmaplus.com.ar/labial-liquido-maybelline-superstay-vinyl-ink/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Maybelline Rubor Líquido Face Sunkisser Matte Blush</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>32995</v>
+      </c>
+      <c r="C15" t="n">
+        <v>32995</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.farmacity.com/rubor-liquido-maybelline-sunkisser-mate-x-4-7-ml/p</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>32990</v>
+      </c>
+      <c r="G15" t="n">
+        <v>32990</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.farmaplus.com.ar/maybelline-rubor-liquido-sunkisser-matte-blush/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Base De Maquillaje Maybelline Fit Me</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Serum Hyalu B5 La Roche Posay con Ácido Hialurónico x 30 ml</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>127171</v>
+      </c>
+      <c r="C17" t="n">
+        <v>127171</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.farmacity.com/serum-hyalu-b5-la-roche-posay-con-acido-hialuronico-x-30-ml/p</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>110816</v>
+      </c>
+      <c r="G17" t="n">
+        <v>110816</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.farmaplus.com.ar/la-roche-posay-hyalu-b5-serum-antiarrugas/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Serum Facial Cetaphil Vitamina C x 30 ml</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>51860</v>
+      </c>
+      <c r="G18" t="n">
+        <v>51860</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.farmaplus.com.ar/cetaphil-serum-vitamina-c-30-ml/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6817</v>
+        <v>7303</v>
       </c>
       <c r="G2" t="n">
         <v>9738</v>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>25.01</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>21823</v>
+        <v>20368</v>
       </c>
       <c r="G6" t="n">
         <v>29097</v>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -634,13 +634,13 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>151697</v>
+        <v>106188</v>
       </c>
       <c r="G8" t="n">
         <v>151697</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61076</v>
+        <v>42753</v>
       </c>
       <c r="C9" t="n">
         <v>61076</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61076</v>
+        <v>42753</v>
       </c>
       <c r="G9" t="n">
         <v>61076</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -694,13 +694,13 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>37950</v>
+        <v>41746</v>
       </c>
       <c r="G10" t="n">
         <v>75901</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40950</v>
+        <v>30712</v>
       </c>
       <c r="C11" t="n">
         <v>40950</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>40950</v>
+        <v>30712</v>
       </c>
       <c r="G11" t="n">
         <v>40950</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -784,13 +784,13 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>18144</v>
+        <v>32990</v>
       </c>
       <c r="G14" t="n">
         <v>32990</v>
       </c>
       <c r="H14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>127171</v>
+        <v>89020</v>
       </c>
       <c r="C17" t="n">
         <v>127171</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>110816</v>
+        <v>77571</v>
       </c>
       <c r="G17" t="n">
         <v>110816</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -894,13 +894,13 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>51860</v>
+        <v>38895</v>
       </c>
       <c r="G18" t="n">
         <v>51860</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -509,10 +509,10 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>9898</v>
+        <v>10990</v>
       </c>
       <c r="G3" t="n">
-        <v>9898</v>
+        <v>10990</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>52000</v>
+        <v>36400</v>
       </c>
       <c r="G5" t="n">
         <v>52000</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20367</v>
+        <v>20958</v>
       </c>
       <c r="C6" t="n">
-        <v>29096</v>
+        <v>29940</v>
       </c>
       <c r="D6" t="n">
         <v>30</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20368</v>
+        <v>20959</v>
       </c>
       <c r="G6" t="n">
-        <v>29097</v>
+        <v>29941</v>
       </c>
       <c r="H6" t="n">
         <v>30</v>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +466,26 @@
           <t>link_farmaplus</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>producto</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>promo_farmacity</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>promo_farmaplus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -497,6 +521,10 @@
           <t>https://www.farmaplus.com.ar/tortulan-desmaquillante-bifasico-de-ojos-y-rostro-x-150ml-barr/p</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +550,10 @@
           <t>https://www.farmaplus.com.ar/mascarilla-elvive-dream-liso-300g/p</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -537,6 +569,10 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -572,6 +608,10 @@
           <t>https://www.farmaplus.com.ar/caviahue-contorno-de-ojos-con-vitamina-k3-15-gr-barr/p</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,6 +647,10 @@
           <t>https://www.farmaplus.com.ar/dermaglos-bb-cream-facial-con-color-tono-claro-fps30-50-g-barr/p</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,6 +666,10 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -647,6 +695,10 @@
           <t>https://www.farmaplus.com.ar/la-roche-posay-mela-b3-serum-antimanchas-30ml-piel-mixta/p</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -682,6 +734,10 @@
           <t>https://www.farmaplus.com.ar/gel-exfoliante-suave-isdin-acniben-teen-skin-100ml/p</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -707,6 +763,10 @@
           <t>https://www.farmaplus.com.ar/protector-solar-eucerin-sun-cc-cream-fps50-con-color-x-50ml-barr/p</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -742,6 +802,10 @@
           <t>https://www.farmaplus.com.ar/cetaphil-limpiador-exfoliante-suave-236ml/p</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -757,6 +821,10 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -772,6 +840,10 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -797,6 +869,10 @@
           <t>https://www.farmaplus.com.ar/labial-liquido-maybelline-superstay-vinyl-ink/p</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -832,6 +908,10 @@
           <t>https://www.farmaplus.com.ar/maybelline-rubor-liquido-sunkisser-matte-blush/p</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -847,6 +927,10 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -882,6 +966,10 @@
           <t>https://www.farmaplus.com.ar/la-roche-posay-hyalu-b5-serum-antiarrugas/p</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -907,6 +995,133 @@
           <t>https://www.farmaplus.com.ar/cetaphil-serum-vitamina-c-30-ml/p</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>$ 15.906$ 26.510</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.wishlist":{},"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>$ 43.922$ 79.859</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.google-search-console":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.wishlist":{},"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.wishlist":{},"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,6 +1126,129 @@
       </c>
       <c r="M21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>$ 15.906$ 26.510</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.wishlist":{},"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>$ 43.922$ 79.859</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{},"vtex.hotjar":{},"farmacityar.vtex-ads":{},"vtex.vtex-ads":{},"vtex.google-search-console":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"vtex.google-tag-manager":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.wishlist":{},"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="1" t="n">
         <v>46089</v>
       </c>
       <c r="K22" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" s="2" t="n">
+      <c r="J23" s="1" t="n">
         <v>46089</v>
       </c>
       <c r="K23" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="1" t="n">
         <v>46089</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -1248,6 +1248,129 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>$ 15.906$ 26.510</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>$ 43.922$ 79.859</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.wishlist":{},"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="1" t="n">
         <v>46090</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="1" t="n">
         <v>46090</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" s="2" t="n">
+      <c r="J27" s="1" t="n">
         <v>46090</v>
       </c>
       <c r="K27" t="inlineStr">
@@ -1371,6 +1371,129 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>$ 15.906$ 26.510</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.wishlist":{},"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>$ 43.922$ 79.859</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.hotjar":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.wishlist":{},"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{}}}</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" s="2" t="n">
+      <c r="J28" s="1" t="n">
         <v>46091</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" s="2" t="n">
+      <c r="J29" s="1" t="n">
         <v>46091</v>
       </c>
       <c r="K29" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="1" t="n">
         <v>46091</v>
       </c>
       <c r="K30" t="inlineStr">
@@ -1494,6 +1494,129 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>$ 15.906$ 26.510</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>$ 43.922$ 79.859</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#sorteo-dioxaflex":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" s="2" t="n">
+      <c r="J31" s="1" t="n">
         <v>46092</v>
       </c>
       <c r="K31" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="1" t="n">
         <v>46092</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
+      <c r="J33" s="1" t="n">
         <v>46092</v>
       </c>
       <c r="K33" t="inlineStr">
@@ -1617,6 +1617,129 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>$ 15.906$ 26.510</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>$ 43.922$ 79.859</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="K34" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" s="2" t="n">
+      <c r="J35" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="K35" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" s="2" t="n">
+      <c r="J36" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -1740,6 +1740,129 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>$ 15.906$ 26.510</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>$ 43.922$ 79.859</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
+      <c r="J37" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="J38" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="J39" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="K39" t="inlineStr">
@@ -1863,6 +1863,129 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>$ 15.906$ 26.510</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtex.vtex-ads":{},"vtex.google-search-console":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>$ 43.922$ 79.859</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtex.vtex-ads":{},"vtex.google-search-console":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtex.vtex-ads":{},"vtex.google-search-console":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
+      <c r="J40" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="K40" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" s="2" t="n">
+      <c r="J41" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="K41" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" s="2" t="n">
+      <c r="J42" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="K42" t="inlineStr">
@@ -1986,6 +1986,129 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>$ 15.906$ 26.510</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>$ 43.922$ 79.859</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" s="2" t="n">
+      <c r="J43" s="1" t="n">
         <v>46096</v>
       </c>
       <c r="K43" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
+      <c r="J44" s="1" t="n">
         <v>46096</v>
       </c>
       <c r="K44" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="J45" s="1" t="n">
         <v>46096</v>
       </c>
       <c r="K45" t="inlineStr">
@@ -2109,6 +2109,121 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>$ 14.580$ 26.510</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>$ 39.929$ 79.859</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
+      <c r="J46" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="K46" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" s="2" t="n">
+      <c r="J47" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="K47" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
+      <c r="J48" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="K48" t="inlineStr">
@@ -2224,6 +2224,129 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>$ 14.580$ 26.510</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.hotjar":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>$ 39.929$ 79.859</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtex.google-search-console":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtex.google-search-console":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
+      <c r="J49" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="K49" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" s="2" t="n">
+      <c r="J50" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="K50" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" s="2" t="n">
+      <c r="J51" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="K51" t="inlineStr">
@@ -2347,6 +2347,129 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>$ 14.580$ 26.510</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.viewed-products":{},"vtex.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>$ 39.929$ 79.859</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.viewed-products":{},"vtex.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.viewed-products":{},"vtex.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" s="2" t="n">
+      <c r="J52" s="1" t="n">
         <v>46099</v>
       </c>
       <c r="K52" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" s="2" t="n">
+      <c r="J53" s="1" t="n">
         <v>46099</v>
       </c>
       <c r="K53" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" s="2" t="n">
+      <c r="J54" s="1" t="n">
         <v>46099</v>
       </c>
       <c r="K54" t="inlineStr">
@@ -2470,6 +2470,129 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>$ 14.580$ 26.510</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.google-search-console":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>$ 39.929$ 79.859</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.viewed-products":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.google-search-console":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{}}}</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" s="2" t="n">
+      <c r="J55" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="K55" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="K56" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" s="2" t="n">
+      <c r="J57" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="K57" t="inlineStr">
@@ -2593,6 +2593,129 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>$ 14.580$ 26.510</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{},"vtex.google-search-console":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>$ 39.929$ 79.859</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{},"vtex.google-search-console":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtex.google-search-console":{},"farmacityar.vtex-ads":{},"vtex.hotjar":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" s="2" t="n">
+      <c r="J58" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="K58" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" s="2" t="n">
+      <c r="J59" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="K59" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" s="2" t="n">
+      <c r="J60" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="K60" t="inlineStr">
@@ -2716,6 +2716,129 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>$ 14.580$ 26.510</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>$ 39.929$ 79.859</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" s="2" t="n">
+      <c r="J61" s="1" t="n">
         <v>46102</v>
       </c>
       <c r="K61" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" s="2" t="n">
+      <c r="J62" s="1" t="n">
         <v>46102</v>
       </c>
       <c r="K62" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" s="2" t="n">
+      <c r="J63" s="1" t="n">
         <v>46102</v>
       </c>
       <c r="K63" t="inlineStr">
@@ -2839,6 +2839,129 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>$ 14.580$ 26.510</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.google-search-console":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>$ 39.929$ 79.859</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.google-search-console":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.google-search-console":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" s="2" t="n">
+      <c r="J64" s="1" t="n">
         <v>46103</v>
       </c>
       <c r="K64" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" s="2" t="n">
+      <c r="J65" s="1" t="n">
         <v>46103</v>
       </c>
       <c r="K65" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" s="2" t="n">
+      <c r="J66" s="1" t="n">
         <v>46103</v>
       </c>
       <c r="K66" t="inlineStr">
@@ -2962,6 +2962,129 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>$ 14.580$ 26.510</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>$ 39.929$ 79.859</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" s="2" t="n">
+      <c r="J67" s="1" t="n">
         <v>46104</v>
       </c>
       <c r="K67" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="1" t="n">
         <v>46104</v>
       </c>
       <c r="K68" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" s="2" t="n">
+      <c r="J69" s="1" t="n">
         <v>46104</v>
       </c>
       <c r="K69" t="inlineStr">
@@ -3085,6 +3085,129 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>$ 14.580$ 26.510</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.viewed-products":{},"vtex.agentic-cx":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>$ 39.929$ 79.859</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.viewed-products":{},"vtex.agentic-cx":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.viewed-products":{},"vtex.agentic-cx":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" s="2" t="n">
+      <c r="J70" s="1" t="n">
         <v>46105</v>
       </c>
       <c r="K70" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" s="2" t="n">
+      <c r="J71" s="1" t="n">
         <v>46105</v>
       </c>
       <c r="K71" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" s="2" t="n">
+      <c r="J72" s="1" t="n">
         <v>46105</v>
       </c>
       <c r="K72" t="inlineStr">
@@ -3208,6 +3208,129 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>$ 26.510</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"vtex.agentic-cx":{},"vtex.hotjar":{},"farmacityar.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtex.request-capture":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>$ 79.859</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"vtex.agentic-cx":{},"vtex.hotjar":{},"farmacityar.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtex.request-capture":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"vtex.agentic-cx":{},"vtex.hotjar":{},"farmacityar.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtex.request-capture":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" s="2" t="n">
+      <c r="J73" s="1" t="n">
         <v>46106</v>
       </c>
       <c r="K73" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" s="2" t="n">
+      <c r="J74" s="1" t="n">
         <v>46106</v>
       </c>
       <c r="K74" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" s="2" t="n">
+      <c r="J75" s="1" t="n">
         <v>46106</v>
       </c>
       <c r="K75" t="inlineStr">
@@ -3331,6 +3331,129 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>$ 26.510</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>$ 79.859</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" s="2" t="n">
+      <c r="J76" s="1" t="n">
         <v>46107</v>
       </c>
       <c r="K76" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" s="2" t="n">
+      <c r="J77" s="1" t="n">
         <v>46107</v>
       </c>
       <c r="K77" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" s="2" t="n">
+      <c r="J78" s="1" t="n">
         <v>46107</v>
       </c>
       <c r="K78" t="inlineStr">
@@ -3454,6 +3454,129 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>$ 26.510</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.hotjar":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>$ 79.859</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.agentic-cx":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.hotjar":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" s="2" t="n">
+      <c r="J79" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="K79" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" s="2" t="n">
+      <c r="J80" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="K80" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" s="2" t="n">
+      <c r="J81" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="K81" t="inlineStr">
@@ -3577,6 +3577,121 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>$ 79.859</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3596,7 +3596,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" s="2" t="n">
+      <c r="J82" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="K82" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" s="2" t="n">
+      <c r="J83" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="K83" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" s="2" t="n">
+      <c r="J84" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="K84" t="inlineStr">
@@ -3692,6 +3692,129 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>$ 26.510</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>$ 79.859</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"vtex.google-search-console":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" s="2" t="n">
+      <c r="J85" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="K85" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" s="2" t="n">
+      <c r="J86" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="K86" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" s="2" t="n">
+      <c r="J87" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="K87" t="inlineStr">
@@ -3815,6 +3815,129 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>$ 26.510</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"vtex.agentic-cx":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>$ 79.859</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.agentic-cx":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.agentic-cx":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" s="2" t="n">
+      <c r="J88" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="K88" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" s="2" t="n">
+      <c r="J89" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="K89" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" s="2" t="n">
+      <c r="J90" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="K90" t="inlineStr">
@@ -3938,6 +3938,121 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>$ 26.510</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.agentic-cx":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>$ 79.859</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.agentic-cx":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>$ 36.400$ 52.000</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.agentic-cx":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" s="2" t="n">
+      <c r="J91" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K91" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" s="2" t="n">
+      <c r="J92" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K92" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" s="2" t="n">
+      <c r="J93" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K93" t="inlineStr">
@@ -4053,6 +4053,121 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>$ 26.510</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>$ 79.859</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>$ 46.800$ 52.000</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{}}}</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" s="2" t="n">
+      <c r="J94" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="K94" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" s="2" t="n">
+      <c r="J95" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="K95" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" s="2" t="n">
+      <c r="J96" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="K96" t="inlineStr">
@@ -4168,6 +4168,129 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>$ 28.338</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtex.vtex-ads":{},"vtex.agentic-cx":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.hotjar":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>$ 79.859</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtex.vtex-ads":{},"vtex.agentic-cx":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.hotjar":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>$ 46.800$ 52.000</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtex.vtex-ads":{},"vtex.agentic-cx":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.hotjar":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" s="2" t="n">
+      <c r="J97" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="K97" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" s="2" t="n">
+      <c r="J98" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="K98" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" s="2" t="n">
+      <c r="J99" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="K99" t="inlineStr">
@@ -4291,6 +4291,129 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>$ 28.338</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"farmacityar.vtex-ads":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.google-tag-manager":{},"vtex.agentic-cx":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.wishlist":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>$ 83.852</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"farmacityar.vtex-ads":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.google-tag-manager":{},"vtex.agentic-cx":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.wishlist":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>$ 50.400$ 56.000</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.viewed-products":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" s="2" t="n">
+      <c r="J100" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="K100" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" s="2" t="n">
+      <c r="J101" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="K101" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" s="2" t="n">
+      <c r="J102" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="K102" t="inlineStr">
@@ -4414,6 +4414,129 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>$ 19.837$ 28.338</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>$ 54.504$ 83.852</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.hotjar":{},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.viewed-products":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>$ 50.400$ 56.000</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" s="2" t="n">
+      <c r="J103" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="K103" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" s="2" t="n">
+      <c r="J104" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="K104" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" s="2" t="n">
+      <c r="J105" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="K105" t="inlineStr">
@@ -4537,6 +4537,129 @@
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>$ 19.837$ 28.338</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.wishlist":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>$ 54.504$ 83.852</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.wishlist":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>$ 50.400$ 56.000</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{},"vtex.google-search-console":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.wishlist":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" s="2" t="n">
+      <c r="J106" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="K106" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" s="2" t="n">
+      <c r="J107" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="K107" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" s="2" t="n">
+      <c r="J108" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="K108" t="inlineStr">
@@ -4660,6 +4660,129 @@
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>$ 19.837$ 28.338</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtex.agentic-cx":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.wishlist":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>$ 54.504$ 83.852</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtex.agentic-cx":{},"vtex.google-search-console":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.wishlist":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>$ 50.400$ 56.000</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.hotjar":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.request-capture":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" s="2" t="n">
+      <c r="J109" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="K109" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" s="2" t="n">
+      <c r="J110" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="K110" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" s="2" t="n">
+      <c r="J111" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="K111" t="inlineStr">
@@ -4783,6 +4783,129 @@
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>$ 19.837$ 28.338</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>$ 54.504$ 83.852</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>$ 50.400$ 56.000</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtexbr.tiktok-tbp":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{}}}</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" s="2" t="n">
+      <c r="J112" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="K112" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" s="2" t="n">
+      <c r="J113" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="K113" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" s="2" t="n">
+      <c r="J114" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="K114" t="inlineStr">
@@ -4906,6 +4906,129 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>$ 19.837$ 28.338</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.agentic-cx":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>$ 54.504$ 83.852</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.agentic-cx":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>$ 50.400$ 56.000</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.agentic-cx":{},"vtex.google-search-console":{},"vtex.google-tag-manager":{},"vtexbr.tiktok-tbp":{},"vtex.vtex-ads":{},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtex.viewed-products":{},"vtex.hotjar":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" s="2" t="n">
+      <c r="J115" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="K115" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" s="2" t="n">
+      <c r="J116" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="K116" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" s="2" t="n">
+      <c r="J117" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="K117" t="inlineStr">
@@ -5029,6 +5029,129 @@
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>$ 19.837$ 28.338</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>$ 54.504$ 83.852</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>$ 53.100$ 59.000</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"farmacityar.vtex-ads":{},"vtex.google-tag-manager":{},"vtex.request-capture":{},"vtex.google-search-console":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{},"vtex.hotjar":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" s="2" t="n">
+      <c r="J118" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="K118" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" s="2" t="n">
+      <c r="J119" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="K119" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" s="2" t="n">
+      <c r="J120" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="K120" t="inlineStr">
@@ -5152,6 +5152,129 @@
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>$ 19.837$ 28.338</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>$ 54.504$ 83.852</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>$ 53.100$ 59.000</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-search-console":{},"farmacityar.vtex-ads":{},"vtex.request-capture":{},"vtex.hotjar":{},"vtex.google-tag-manager":{},"vtex.viewed-products":{},"vtexbr.tiktok-tbp":{},"vtex.agentic-cx":{},"vtex.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" s="2" t="n">
+      <c r="J121" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="K121" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" s="2" t="n">
+      <c r="J122" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="K122" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" s="2" t="n">
+      <c r="J123" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="K123" t="inlineStr">
@@ -5275,6 +5275,129 @@
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>$ 19.837$ 28.338</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.agentic-cx":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>$ 54.504$ 83.852</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.hotjar":{},"vtex.agentic-cx":{},"vtex.google-search-console":{},"vtex.viewed-products":{},"vtex.google-tag-manager":{},"vtex.vtex-ads":{},"farmacityar.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.request-capture":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>$ 53.100$ 59.000</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Caviahue Contorno de Ojos</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.request-capture":{},"farmacityar.vtex-ads":{},"vtexbr.tiktok-tbp":{},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.hotjar":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtex.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"234036","slug":"contorno-de-ojos-caviahue-vitamina-k3-x-15-g"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{}}}</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparador_precios.xlsx
+++ b/comparador_precios.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" s="2" t="n">
+      <c r="J124" s="1" t="n">
         <v>46123</v>
       </c>
       <c r="K124" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" s="2" t="n">
+      <c r="J125" s="1" t="n">
         <v>46123</v>
       </c>
       <c r="K125" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" s="2" t="n">
+      <c r="J126" s="1" t="n">
         <v>46123</v>
       </c>
       <c r="K126" t="inlineStr">
@@ -5398,6 +5398,129 @@
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>$ 19.837$ 28.338</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Nivea Sun Tono Medio</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.request-capture":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"244913","slug":"protector-solar-nivea-sun-tono-medio-fps-50-x-40-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-hongos-adaptogenos":{},"vtex.store@2.x:store.custom#hot-sale-prueba":{},"vtex.store@2.x:store.custom#sorteo-mastercard":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital-app":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cancer-de-mama":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-2x1":{},"vtex.store@2.x:store.custom#lanzamientos-nuxe":{},"vtex.store@2.x:store.custom#lanzamientos-doveuvrepair":{},"vtex.store@2.x:store.custom#auto-pickup-farmacity":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-diabetes":{},"vtex.store@2.x:store.custom#sorteo-rimmel":{},"vtex.store@2.x:store.custom#ofertas-black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-black-friday-bebes":{},"vtex.store@2.x:store.custom#ofertas-black-friday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta-50off":{},"vtex.store@2.x:store.custom#ofertas-black-friday-hasta2x1":{},"vtex.store@2.x:store.custom#vih-huesped":{},"vtex.store@2.x:store.custom#Farmacity-politicas-de-privacidad":{},"vtex.store@2.x:store.custom#lanzamientos-dove-oleos-corporales":{},"vtex.store@2.x:store.custom#suplementos":{},"vtex.store@2.x:store.custom#festival-farmacity":{},"vtex.store@2.x:store.custom#k-beauty":{},"vtex.store@2.x:store.custom#ofertas-farma-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble ":{},"vtex.store@2.x:store.custom#lanzamientos-colossalbubble":{},"vtex.store@2.x:store.custom#brilla-a-tu-manera":{},"vtex.store@2.x:store.custom#lanzamientos-nuevohyalub5serum":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-antigripal":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-cannabis-medicinal":{},"vtex.store@2.x:store.custom#ofertas-pure-wellness":{},"vtex.store@2.x:store.custom#lanzamientos-rimmelmegalift":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-centella-asiatica":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-bakuchiol":{},"vtex.store@2.x:store.custom#blog-dermocosmetica-temporada-de-peeling":{}}}</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>$ 0</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Favoritos</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>$ 54.504$ 83.852</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Ofertas</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Vichy Capital Soleil</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>__RUNTIME__ = {"account":"farmacityar","amp":false,"assetServerPublishedHost":"farmacityar.vtexassets.com","assetServerLinkedHost":"www.farmacity.com","bindingChanged":false,"binding":{"id":"3f1f8de4-5030-4794-a242-443b8f589575","canonicalBaseAddress":"farmacityar.myvtex.com\u002F"},"culture":{"availableLocales":[],"country":"ARG","currency":"ARS","language":"es","locale":"es-AR","customCurrencyDecimalDigits":0,"customCurrencySymbol":"$"},"production":true,"query":{},"settings":{"vtex.store":{"enableOrderFormOptimization":false,"enableServiceWorker":true,"enableCriticalCSS":true,"enableCriticalCSSOnSearch":false,"enableCriticalCSSOnCustom":false,"enableCriticalCSSOnProduct":false,"enableCSSConcatenation":true,"enablePrefetch":true,"enableLazyRuntime":true,"enableMenuRenderingOptimization":true,"enableSearchRenderingOptimization":true,"enableAsyncScripts":true,"enableConcurrentMode":true,"enableFiltersFetchOptimization":false,"enableFullSSROnProduct":false,"enableLazyFooter":true,"enableLazyFold":true,"enablePageNumberTitle":false,"canonicalWithoutUrlParams":false,"removeStoreNameTitle":false,"enableCustomCurrencySymbol":false,"fetchSponsoredProductsOnSearch":false,"bindingBounded":false,"faviconLinks":[{"rel":"shortcut icon","href":"https:\u002F\u002Ffarmacityar.vtexassets.com\u002Farquivos\u002Ffavicon2024.png"}],"storeName":"Farmacity","titleTag":"Belleza, cuidado personal, dermocosmética y farmacia - Farmacity ","metaTagRobots":"","metaTagDescription":"¡Ingresá a la tienda online de Farmacity y encontrá una solución simple a tus necesidades cotidianas! Tenemos productos de: belleza, dermocosmética y farmacia.","publisherId":"92f10352-44b1-4737-9c50-563669c7efe5"},"vtex.google-tag-manager":{},"vtex.google-search-console":{},"vtex.request-capture":{},"vtex.agentic-cx":{},"vtex.viewed-products":{},"vtex.hotjar":{},"vtex.vtex-ads":{},"vtexbr.tiktok-tbp":{},"farmacityar.vtex-ads":{}},"workspace":"master","workspaceCookie":null,"route":{"domain":"store","id":"store.product","params":{"id":"246052","slug":"aceite-solar-invisible-vichy-capital-soleil-cell-protect-spf-50-x-200-ml"}},"pages":{"store.storelocator":{},"store.storedetail":{},"store.wishlist":{},"store.home":{},"store.account":{},"store.login":{},"store.product":{},"store.search":{},"store.search#brand":{},"store.search#department":{},"store.search#category":{},"store.search#subcategory":{},"store.search#configurable":{},"store.orderplaced":{},"store.offline":{},"store.custom":{},"store.not-found#product":{},"store.not-found#search":{},"store.custom#trabaja-nosotros":{},"store.custom#catalog":{},"store.custom#promocionesOfertas":{},"store.custom#tuf":{},"store.custom#com-eje":{},"store.custom#prov":{},"store.custom#legal":{},"store.custom#bebes":{},"store.custom#modularv2":{},"store.custom#modularv3":{},"store.custom#free-shipping-config":{},"store.custom#checkout-config":{},"store.custom#ship-cost":{},"store.custom#belleza":{},"store.custom#encuentra-medicamentos":{},"store.custom#promocion-2x1":{},"store.custom#marcas":{},"store.custom#dermocosmetica":{},"store.custom#cuidado-personal":{},"store.custom#hogar-y-alimentos":{},"store.custom#salud-y-farmacia":{},"store.custom#maquillaje":{},"store.custom#accesorios-de-belleza":{},"store.custom#electro-belleza":{},"store.custom#pelo":{},"store.custom#cuidado-personal-cuidado-oral":{},"store.custom#higiene-personal":{},"store.custom#adultos":{},"store.custom#repelentes":{},"store.custom#nutricion-infantil":{},"store.custom#lactancia":{},"store.custom#maternidad":{},"store.custom#higiene-del-bebe":{},"store.custom#cuidado-del-bebe":{},"store.custom#alimentacion-saludable":{},"store.custom#infusiones":{},"store.custom#limpieza":{},"store.custom#electro-hogar":{},"store.custom#alimentos-y-bebidas":{},"store.custom#papeles":{},"store.custom#desodorantes-de-ambiente":{},"store.custom#bazar":{},"store.custom#farmacia":{},"store.custom#nutricion-y-deportes":{},"store.custom#electrosalud":{},"store.custom#bienestar-sexual":{},"store.custom#labios":{},"store.custom#ojos":{},"store.custom#rostron3":{},"store.custom#uñas":{},"store.custom#hombres":{},"store.custom#colonias-y-body-splash":{},"store.custom#cremas-corporales":{},"store.custom#cremas-faciales":{},"store.custom#proteccion-solar":{},"store.custom#accesorios-de-pelo":{},"store.custom#accesorios-de-maquillaje":{},"store.custom#cortadoras-y-afeitadoras":{},"store.custom#masajeadores-y-exfoliadores":{},"store.custom#planchas-y-bucleras":{},"store.custom#secadores":{},"store.custom#depiladoras":{},"store.custom#shampoo-y-acondicionador":{},"store.custom#reparacion-y-tratamiento":{},"store.custom#modelado-y-peinado":{},"store.custom#coloracion-y-oxidantes":{},"store.custom#professional":{},"store.custom#revitalifretinol":{},"store.custom#revitalifhialuro":{},"store.custom#agua-termal":{},"store.custom#anti-acne":{},"store.custom#anti-edad":{},"store.custom#anti-manchas":{},"store.custom#hidratacion":{},"store.custom#cicatrizantes":{},"store.custom#higiene":{},"store.custom#piel-atopica":{},"store.custom#piel-seca":{},"store.custom#anti-celuliticos":{},"store.custom#autobronceante-y-post-solar":{},"store.custom#pediculosis":{},"store.custom#alimentos-infantiles":{},"store.custom#leches-y-formulas":{},"store.custom#accesorios":{},"store.custom#mamaderas-y-tetinas":{},"store.custom#esterilizadores":{},"store.custom#sacaleches-y-accesorios":{},"store.custom#calienta-mamaderas":{},"store.custom#apositos-y-protectores-mamarios":{},"store.custom#cremas":{},"store.custom#fajas":{},"store.custom#pezoneras":{},"store.custom#pañales":{},"store.custom#toallas-humedas":{},"store.custom#oleos-y-algodon":{},"store.custom#cambiadores":{},"store.custom#bano-del-bebe":{},"store.custom#chupetes-y-mordillos":{},"store.custom#c-b-accesorios":{},"store.custom#cereales-semillas-y-frutos-secos":{},"store.custom#dulces-y-mermeladas":{},"store.custom#galletitas-y-tostadas":{},"store.custom#snacks-saludables":{},"store.custom#celiacos":{},"store.custom#cafe":{},"store.custom#te":{},"store.custom#yerba":{},"store.custom#accesorios-de-limpieza":{},"store.custom#bano":{},"store.custom#cocina":{},"store.custom#cuidado-de-la-ropa":{},"store.custom#desinfeccion":{},"store.custom#jugueras-y-exprimidores":{},"store.custom#pavas":{},"store.custom#planchas":{},"store.custom#procesadoras-y-minipimer":{},"store.custom#tostadoras-y-sandwicheras":{},"store.custom#golosinas":{},"store.custom#bebidas":{},"store.custom#azucar-miel-y-endulzantes":{},"store.custom#caldos-sopas-y-pures":{},"store.custom#pequeñas-porciones":{},"store.custom#pañuelos-descartables":{},"store.custom#papel-higienico":{},"store.custom#rollos-de-cocina-y-servilletas":{},"store.custom#aromatizadores":{},"store.custom#difusores":{},"store.custom#primeros-auxilios":{},"store.custom#diabetes":{},"store.custom#optica":{},"store.custom#pedicos":{},"store.custom#suplementos-dietarios":{},"store.custom#suplementos-nutricionales":{},"store.custom#suplementos-deportivos":{},"store.custom#proteccion-y-recuperacion":{},"store.custom#fitness":{},"store.custom#tensiometros":{},"store.custom#nebulizadores":{},"store.custom#balanzas":{},"store.custom#termometros":{},"store.custom#almohadillas-termicas":{},"store.custom#preservativos":{},"store.custom#lubricantes":{},"store.custom#estimuladores-sexuales":{},"store.custom#cannabis-medicinal":{},"store.custom#bienestar-en-casa":{},"store.custom#gabinete-especializado-en-salud":{},"store.custom#event-plate":{},"store.custom#reserva-de-medicamento":{},"store.custom#folleto":{},"store.custom#sortableLayout":{},"store.custom#double-banner-bg":{},"store.custom#landing-sorteo":{},"store.custom#landing-login":{},"store.custom#viewed-products":{},"store.custom#blog":{},"store.custom#query-sent":{},"store.custom#query-sent-app":{},"store.custom#contact":{},"store.custom#contact-app":{},"store.custom#regret-button-form":{},"store.custom#regret-button-form-app":{},"store.custom#nuestra-empresa":{},"store.custom#terminos-condiciones":{},"store.custom#preguntas-frecuentes":{},"store.custom#locals":{},"store.custom#locals-app":{},"store.custom#payment-methods":{},"store.custom#abandoned-cart":{},"vtex.store@2.x:store.custom#promociones-cuidado-de-la-piel":{},"vtex.store@2.x:store.custom#lanzamientos-theicon":{},"vtex.store@2.x:store.custom#descuentos-jugados":{},"vtex.store@2.x:store.custom#lanzamientos-elvive":{},"vtex.store@2.x:store.custom#promociones--espacial2x1":{},"vtex.store@2.x:store.custom#lanzamientos-plenitud":{},"vtex.store@2.x:store.custom#cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-cuidado-personal":{},"vtex.store@2.x:store.custom#promociones-especial-solares-ws":{},"store.custom#perfumes-y-fragancias":{},"store.custom#cuidado-de-la-piel":{},"store.custom#rostro":{},"store.custom#corporal":{},"store.custom#solar":{},"store.custom#dermocosmetica-pelo":{},"vtex.store@2.x:store.custom#especial-verano":{},"vtex.store@2.x:store.custom#test-mp":{},"vtex.store@2.x:store.custom#farmacity-promociones-ws":{},"vtex.store@2.x:store.custom#semana-tuf":{},"vtex.store@2.x:store.custom#consumo-consciente":{},"vtex.store@2.x:store.custom#lanzamientos-johnsonsbaby":{},"vtex.store@2.x:store.custom#prueba-modular":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-viajero":{},"vtex.store@2.x:store.custom#hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#hot-sale-belleza":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-electro":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-alimentos":{},"vtex.store@2.x:store.custom#hot-sale-nuestras-marcas":{},"vtex.store@2.x:store.custom#hot-sale-bebes":{},"vtex.store@2.x:store.custom#hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#hot-sale":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#coleccion-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#cuponera":{},"vtex.store@2.x:store.custom#coleccion-hot-sale":{},"vtex.store@2.x:store.custom#farmacity-wow":{},"vtex.store@2.x:store.custom#dia-del-padre":{},"vtex.store@2.x:store.custom#libro-de-quejas-digital":{},"vtex.store@2.x:store.custom#farma-sale":{},"vtex.store@2.x:store.custom#coleccion-imperdibles-de-dermo":{},"vtex.store@2.x:store.custom#evento-viralbeauty":{},"vtex.store@2.x:store.custom#farmacity-enjoy-instructivo-tampones":{},"vtex.store@2.x:store.custom#beauty-week":{},"vtex.store@2.x:store.custom#lanzamientos-doveserumcremas":{},"vtex.store@2.x:store.custom#salud-y-farmacia-salud-del-corazon":{},"vtex.store@2.x:store.custom#coleccion-dia-de-la-maternidad":{},"vtex.store@2.x:store.custom#cyber-monday-nuestras-marcas":{},"vtex.store@2.x:store.custom#cyber-monday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#cyber-monday-bebes":{},"vtex.store@2.x:store.custom#cyber-monday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#cyber-monday-belleza":{},"vtex.store@2.x:store.custom#cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#lanzamientos-isdin":{},"vtex.store@2.x:store.custom#tengotuvetendre":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-bebes":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-suplementos":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday-proteccion-solar":{},"vtex.store@2.x:store.custom#coleccion-especial-solares":{},"vtex.store@2.x:store.custom#ofertas-cyber-monday":{},"vtex.store@2.x:store.custom#black-friday-nutricion-y-salud":{},"vtex.store@2.x:store.custom#black-friday-nuestras-marcas":{},"vtex.store@2.x:store.custom#black-friday-bebes":{},"vtex.store@2.x:store.custom#black-friday-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#black-friday-dermocosmetica":{},"vtex.store@2.x:store.custom#black-friday-belleza":{},"vtex.store@2.x:store.custom#ofertas-black-friday":{},"vtex.store@2.x:store.custom#ofertas-black-friday-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-black-friday-cuidado-capilar":{},"vtex.store@2.x:store.custom#ofertas-black-friday-proteccion-solar":{},"vtex.store@2.x:store.custom#black-friday":{},"vtex.store@2.x:store.custom#especial-regaleria":{},"vtex.store@2.x:store.custom#vih-intransmisible":{},"vtex.store@2.x:store.custom#ofertas-nuestras-marcas":{},"vtex.store@2.x:store.custom#anticonceptivo-de-emergencia":{},"vtex.store@2.x:store.custom#ofertas-farma-sale":{},"vtex.store@2.x:store.custom#ofertas-semana-tuf":{},"store.custom#mujeres":{},"vtex.store@2.x:store.custom#medicamentos":{},"vtex.store@2.x:store.custom#lanzamientos-GUM":{},"vtex.store@2.x:store.custom#cupones-dermatologicos":{},"vtex.store@2.x:store.custom#lanzamientos-colgatetotal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-dermocosmetica":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-maquillaje":{},"vtex.store@2.x:store.custom#ofertas-hot-sale":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-personal":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-bebes":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-suplementos":{},"vtex.store@2.x:store.custom#ofertas-hot-sale-cuidado-capilar":{},"vtex.store@2.x:store.custom#hot-sale-nutricion-y-salud":{},"vtex.store@2.x:store.custom#hot-sale-hogar-y-alimentos":{},"vtex.store@2.x:store.custom#hablalo":{},"vtex.store@2.x:store.custom#salud-y-farmacia-vacunacion-pami":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sarampion":{},"vtex.store@2.x:store.custom#lanzamientos-eucerin-hydro-fluid":{},"vtex.store@2.x:store.custom#ofertas-dia-de-la-paternidad":{},"vtex.store@2.x:store.custom#sorteo-maybelline":{},"vtex.store@2.x:store.custom#salud-y-farmacia-sin-filtro":{},"vtex.store@2.x:store.custom#ofertas-dias-de-pelos":{},"vtex.store@2.x:store.custom#salud-y-farmacia-hepatitis":{},"vtex.store@2.x:store.custom#semana-de-la-amistad":{},"vtex.store@2.x:store.custom#noche-tu-farmacity":{},"vtex.store@2.x:store.custom#marcas-que-te-acompanan":{},"vtex.store@2.x:store.custom#regalo-por-monto":{},"vtex.store@2.x:store.custom#lanzamientos-cerave-airfoam":{},"vtex.store@2.x:store.custom#salud-y-farmacia-herpes-zoster":{},"vtex.store@2.x:store.custom#lanzamientos-anthelios-uv-air":{},"vtex.store@2.x:store.custom#lanzamientos-ledefile":{},"vtex.store@2.x:store.custom#app-farmacity":{},"vtex.store@2.x:store.custom#lanzamientos-allbodydeo":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-dia":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-rutina-de-noche":{},"vtex.store@2.x:store.custom#blog-cuidado-de-la-piel-proteccion-solar":{},"vtex.store@2.x:store.custom#blog-salud-y-farmacia-meningitis":{},"vtex.store@2.